--- a/rules/CORE-000303/negative/01/data/unit-test-coreid-FB0901-negative.xlsx
+++ b/rules/CORE-000303/negative/01/data/unit-test-coreid-FB0901-negative.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="lb.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="fa.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lb.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fa.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +36,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFCC"/>
         <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +94,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,38 +552,598 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Error group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Error level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Row num</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LBTEST</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Albumin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LBTEST</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Alkaline Phosphatase</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LBTEST</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aspartate Aminotransferase</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BASO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LBTEST</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aspartate Aminotransferase</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BASO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LBTEST</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Basophils</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FATESTCD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FATEST</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FATESTCD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FATEST</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FATESTCD</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FATEST</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Counting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FATESTCD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FATEST</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Counted</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FATESTCD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FATEST</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Count</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1620,12 @@
       <c r="D5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>ALB</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Albumin</t>
         </is>
@@ -1155,12 +1724,12 @@
       <c r="D6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>ALB</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Alkaline Phosphatase</t>
         </is>
@@ -1267,12 +1836,12 @@
       <c r="D7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>ALB</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Aspartate Aminotransferase</t>
         </is>
@@ -1374,12 +1943,12 @@
       <c r="D8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>BASO</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Aspartate Aminotransferase</t>
         </is>
@@ -1481,12 +2050,12 @@
       <c r="D9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>BASO</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Basophils</t>
         </is>
@@ -1944,12 +2513,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -2027,12 +2596,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
@@ -2110,12 +2679,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Counting</t>
         </is>
@@ -2185,12 +2754,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Counted</t>
         </is>
@@ -2265,12 +2834,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
